--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -6339,32 +6339,32 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
-      <c r="A99" s="3" t="s">
+    <row r="99" s="1" customFormat="1" spans="1:9">
+      <c r="A99" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D99" s="4">
+      <c r="C99" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D99" s="8">
         <v>2400</v>
       </c>
-      <c r="E99" s="3">
+      <c r="E99" s="7">
         <v>19</v>
       </c>
-      <c r="F99" s="5">
-        <v>0</v>
-      </c>
-      <c r="G99" s="3" t="s">
+      <c r="F99" s="9">
+        <v>0</v>
+      </c>
+      <c r="G99" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H99" s="3" t="s">
+      <c r="H99" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="I99" t="s">
+      <c r="I99" s="1" t="s">
         <v>49</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920"/>
+    <workbookView windowWidth="30240" windowHeight="12900"/>
   </bookViews>
   <sheets>
     <sheet name="关键词清单" sheetId="1" r:id="rId1"/>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -6368,32 +6368,32 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
-      <c r="A100" s="3" t="s">
+    <row r="100" s="1" customFormat="1" spans="1:9">
+      <c r="A100" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D100" s="4">
+      <c r="C100" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D100" s="8">
         <v>2400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="7">
         <v>19</v>
       </c>
-      <c r="F100" s="5">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3" t="s">
+      <c r="F100" s="9">
+        <v>0</v>
+      </c>
+      <c r="G100" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H100" s="3" t="s">
+      <c r="H100" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="I100" t="s">
+      <c r="I100" s="1" t="s">
         <v>97</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12900"/>
+    <workbookView windowWidth="30240" windowHeight="12920"/>
   </bookViews>
   <sheets>
     <sheet name="关键词清单" sheetId="1" r:id="rId1"/>
@@ -7325,32 +7325,32 @@
         <v>335</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
-      <c r="A133" s="3" t="s">
+    <row r="133" s="1" customFormat="1" spans="1:9">
+      <c r="A133" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C133" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D133" s="4">
+      <c r="C133" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D133" s="8">
         <v>1900</v>
       </c>
-      <c r="E133" s="3">
+      <c r="E133" s="7">
         <v>16</v>
       </c>
-      <c r="F133" s="5">
-        <v>0</v>
-      </c>
-      <c r="G133" s="3" t="s">
+      <c r="F133" s="9">
+        <v>0</v>
+      </c>
+      <c r="G133" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H133" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I133" t="s">
+      <c r="H133" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I133" s="1" t="s">
         <v>337</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920"/>
+    <workbookView windowWidth="30240" windowHeight="12900"/>
   </bookViews>
   <sheets>
     <sheet name="关键词清单" sheetId="1" r:id="rId1"/>
@@ -7354,32 +7354,32 @@
         <v>337</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
-      <c r="A134" s="3" t="s">
+    <row r="134" s="1" customFormat="1" spans="1:9">
+      <c r="A134" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C134" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D134" s="4">
+      <c r="C134" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D134" s="8">
         <v>1900</v>
       </c>
-      <c r="E134" s="3">
+      <c r="E134" s="7">
         <v>16</v>
       </c>
-      <c r="F134" s="5">
-        <v>0</v>
-      </c>
-      <c r="G134" s="3" t="s">
+      <c r="F134" s="9">
+        <v>0</v>
+      </c>
+      <c r="G134" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H134" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I134" t="s">
+      <c r="H134" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I134" s="1" t="s">
         <v>339</v>
       </c>
     </row>
@@ -7412,32 +7412,32 @@
         <v>49</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
-      <c r="A136" s="3" t="s">
+    <row r="136" s="1" customFormat="1" spans="1:9">
+      <c r="A136" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C136" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D136" s="4">
+      <c r="C136" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D136" s="8">
         <v>1900</v>
       </c>
-      <c r="E136" s="3">
+      <c r="E136" s="7">
         <v>18</v>
       </c>
-      <c r="F136" s="5">
-        <v>0</v>
-      </c>
-      <c r="G136" s="3" t="s">
+      <c r="F136" s="9">
+        <v>0</v>
+      </c>
+      <c r="G136" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H136" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I136" t="s">
+      <c r="H136" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I136" s="1" t="s">
         <v>342</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -8311,32 +8311,32 @@
         <v>49</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
-      <c r="A167" s="3" t="s">
+    <row r="167" s="1" customFormat="1" spans="1:9">
+      <c r="A167" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="B167" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C167" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D167" s="4">
+      <c r="C167" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D167" s="8">
         <v>1600</v>
       </c>
-      <c r="E167" s="3">
+      <c r="E167" s="7">
         <v>8</v>
       </c>
-      <c r="F167" s="5">
-        <v>0</v>
-      </c>
-      <c r="G167" s="3" t="s">
+      <c r="F167" s="9">
+        <v>0</v>
+      </c>
+      <c r="G167" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H167" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I167" t="s">
+      <c r="H167" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I167" s="1" t="s">
         <v>396</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -8340,32 +8340,32 @@
         <v>396</v>
       </c>
     </row>
-    <row r="168" spans="1:9">
-      <c r="A168" s="3" t="s">
+    <row r="168" s="1" customFormat="1" spans="1:9">
+      <c r="A168" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B168" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C168" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D168" s="4">
+      <c r="C168" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D168" s="8">
         <v>1600</v>
       </c>
-      <c r="E168" s="3">
+      <c r="E168" s="7">
         <v>14</v>
       </c>
-      <c r="F168" s="5">
-        <v>0</v>
-      </c>
-      <c r="G168" s="3" t="s">
+      <c r="F168" s="9">
+        <v>0</v>
+      </c>
+      <c r="G168" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H168" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I168" t="s">
+      <c r="H168" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I168" s="1" t="s">
         <v>398</v>
       </c>
     </row>
@@ -8398,32 +8398,32 @@
         <v>401</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
-      <c r="A170" s="3" t="s">
+    <row r="170" s="1" customFormat="1" spans="1:9">
+      <c r="A170" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="B170" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C170" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D170" s="4">
+      <c r="C170" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D170" s="8">
         <v>1600</v>
       </c>
-      <c r="E170" s="3">
+      <c r="E170" s="7">
         <v>14</v>
       </c>
-      <c r="F170" s="5">
-        <v>0</v>
-      </c>
-      <c r="G170" s="3" t="s">
+      <c r="F170" s="9">
+        <v>0</v>
+      </c>
+      <c r="G170" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H170" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I170" t="s">
+      <c r="H170" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I170" s="1" t="s">
         <v>403</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -8485,32 +8485,32 @@
         <v>86</v>
       </c>
     </row>
-    <row r="173" spans="1:9">
-      <c r="A173" s="3" t="s">
+    <row r="173" s="1" customFormat="1" spans="1:9">
+      <c r="A173" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B173" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C173" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D173" s="4">
+      <c r="C173" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D173" s="8">
         <v>1600</v>
       </c>
-      <c r="E173" s="3">
+      <c r="E173" s="7">
         <v>16</v>
       </c>
-      <c r="F173" s="5">
-        <v>0</v>
-      </c>
-      <c r="G173" s="3" t="s">
+      <c r="F173" s="9">
+        <v>0</v>
+      </c>
+      <c r="G173" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H173" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I173" t="s">
+      <c r="H173" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I173" s="1" t="s">
         <v>115</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -8543,61 +8543,61 @@
         <v>408</v>
       </c>
     </row>
-    <row r="175" spans="1:9">
-      <c r="A175" s="3" t="s">
+    <row r="175" s="1" customFormat="1" spans="1:9">
+      <c r="A175" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="B175" s="3" t="s">
+      <c r="B175" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C175" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D175" s="4">
+      <c r="C175" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D175" s="8">
         <v>1600</v>
       </c>
-      <c r="E175" s="3">
+      <c r="E175" s="7">
         <v>17</v>
       </c>
-      <c r="F175" s="5">
-        <v>0</v>
-      </c>
-      <c r="G175" s="3" t="s">
+      <c r="F175" s="9">
+        <v>0</v>
+      </c>
+      <c r="G175" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H175" s="3" t="s">
+      <c r="H175" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="I175" t="s">
+      <c r="I175" s="1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="176" spans="1:9">
-      <c r="A176" s="3" t="s">
+    <row r="176" s="1" customFormat="1" spans="1:9">
+      <c r="A176" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B176" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C176" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D176" s="4">
+      <c r="C176" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D176" s="8">
         <v>1600</v>
       </c>
-      <c r="E176" s="3">
+      <c r="E176" s="7">
         <v>18</v>
       </c>
-      <c r="F176" s="5">
+      <c r="F176" s="9">
         <v>0.34</v>
       </c>
-      <c r="G176" s="3" t="s">
+      <c r="G176" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H176" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I176" t="s">
+      <c r="H176" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I176" s="1" t="s">
         <v>413</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -8601,32 +8601,32 @@
         <v>413</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
-      <c r="A177" s="3" t="s">
+    <row r="177" s="1" customFormat="1" spans="1:9">
+      <c r="A177" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="B177" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C177" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D177" s="4">
+      <c r="C177" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D177" s="8">
         <v>1600</v>
       </c>
-      <c r="E177" s="3">
+      <c r="E177" s="7">
         <v>19</v>
       </c>
-      <c r="F177" s="5">
-        <v>0</v>
-      </c>
-      <c r="G177" s="3" t="s">
+      <c r="F177" s="9">
+        <v>0</v>
+      </c>
+      <c r="G177" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H177" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I177" t="s">
+      <c r="H177" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I177" s="1" t="s">
         <v>415</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -8630,32 +8630,32 @@
         <v>415</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
-      <c r="A178" s="3" t="s">
+    <row r="178" s="1" customFormat="1" spans="1:9">
+      <c r="A178" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="B178" s="3" t="s">
+      <c r="B178" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C178" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D178" s="4">
+      <c r="C178" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D178" s="8">
         <v>1600</v>
       </c>
-      <c r="E178" s="3">
+      <c r="E178" s="7">
         <v>20</v>
       </c>
-      <c r="F178" s="5">
-        <v>0</v>
-      </c>
-      <c r="G178" s="3" t="s">
+      <c r="F178" s="9">
+        <v>0</v>
+      </c>
+      <c r="G178" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H178" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I178" t="s">
+      <c r="H178" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I178" s="1" t="s">
         <v>417</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -9993,32 +9993,32 @@
         <v>505</v>
       </c>
     </row>
-    <row r="225" spans="1:9">
-      <c r="A225" s="3" t="s">
+    <row r="225" s="1" customFormat="1" spans="1:9">
+      <c r="A225" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="B225" s="3" t="s">
+      <c r="B225" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C225" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D225" s="4">
+      <c r="C225" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D225" s="8">
         <v>1300</v>
       </c>
-      <c r="E225" s="3">
+      <c r="E225" s="7">
         <v>17</v>
       </c>
-      <c r="F225" s="5">
-        <v>0</v>
-      </c>
-      <c r="G225" s="3" t="s">
+      <c r="F225" s="9">
+        <v>0</v>
+      </c>
+      <c r="G225" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H225" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I225" t="s">
+      <c r="H225" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I225" s="1" t="s">
         <v>86</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -10022,32 +10022,32 @@
         <v>86</v>
       </c>
     </row>
-    <row r="226" spans="1:9">
-      <c r="A226" s="3" t="s">
+    <row r="226" s="1" customFormat="1" spans="1:9">
+      <c r="A226" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="B226" s="3" t="s">
+      <c r="B226" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C226" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D226" s="4">
+      <c r="C226" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D226" s="8">
         <v>1300</v>
       </c>
-      <c r="E226" s="3">
+      <c r="E226" s="7">
         <v>17</v>
       </c>
-      <c r="F226" s="5">
+      <c r="F226" s="9">
         <v>0.03</v>
       </c>
-      <c r="G226" s="3" t="s">
+      <c r="G226" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H226" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I226" t="s">
+      <c r="H226" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I226" s="1" t="s">
         <v>168</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -10167,32 +10167,32 @@
         <v>49</v>
       </c>
     </row>
-    <row r="231" spans="1:9">
-      <c r="A231" s="3" t="s">
+    <row r="231" s="1" customFormat="1" spans="1:9">
+      <c r="A231" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="B231" s="3" t="s">
+      <c r="B231" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C231" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D231" s="4">
+      <c r="C231" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D231" s="8">
         <v>1300</v>
       </c>
-      <c r="E231" s="3">
+      <c r="E231" s="7">
         <v>19</v>
       </c>
-      <c r="F231" s="5">
-        <v>0</v>
-      </c>
-      <c r="G231" s="3" t="s">
+      <c r="F231" s="9">
+        <v>0</v>
+      </c>
+      <c r="G231" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H231" s="3" t="s">
+      <c r="H231" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="I231" t="s">
+      <c r="I231" s="1" t="s">
         <v>72</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -10196,32 +10196,32 @@
         <v>72</v>
       </c>
     </row>
-    <row r="232" spans="1:9">
-      <c r="A232" s="3" t="s">
+    <row r="232" s="1" customFormat="1" spans="1:9">
+      <c r="A232" s="7" t="s">
         <v>516</v>
       </c>
-      <c r="B232" s="3" t="s">
+      <c r="B232" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C232" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D232" s="4">
+      <c r="C232" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D232" s="8">
         <v>1300</v>
       </c>
-      <c r="E232" s="3">
+      <c r="E232" s="7">
         <v>19</v>
       </c>
-      <c r="F232" s="5">
-        <v>0</v>
-      </c>
-      <c r="G232" s="3" t="s">
+      <c r="F232" s="9">
+        <v>0</v>
+      </c>
+      <c r="G232" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H232" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I232" t="s">
+      <c r="H232" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I232" s="1" t="s">
         <v>517</v>
       </c>
     </row>
@@ -10254,32 +10254,32 @@
         <v>86</v>
       </c>
     </row>
-    <row r="234" spans="1:9">
-      <c r="A234" s="3" t="s">
+    <row r="234" s="1" customFormat="1" spans="1:9">
+      <c r="A234" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="B234" s="3" t="s">
+      <c r="B234" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C234" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D234" s="4">
+      <c r="C234" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D234" s="8">
         <v>1300</v>
       </c>
-      <c r="E234" s="3">
+      <c r="E234" s="7">
         <v>20</v>
       </c>
-      <c r="F234" s="5">
+      <c r="F234" s="9">
         <v>0.02</v>
       </c>
-      <c r="G234" s="3" t="s">
+      <c r="G234" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H234" s="3" t="s">
+      <c r="H234" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="I234" t="s">
+      <c r="I234" s="1" t="s">
         <v>521</v>
       </c>
     </row>
@@ -10312,32 +10312,32 @@
         <v>523</v>
       </c>
     </row>
-    <row r="236" spans="1:9">
-      <c r="A236" s="3" t="s">
+    <row r="236" s="1" customFormat="1" spans="1:9">
+      <c r="A236" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="B236" s="3" t="s">
+      <c r="B236" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C236" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D236" s="4">
+      <c r="C236" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D236" s="8">
         <v>1300</v>
       </c>
-      <c r="E236" s="3">
+      <c r="E236" s="7">
         <v>20</v>
       </c>
-      <c r="F236" s="5">
-        <v>0</v>
-      </c>
-      <c r="G236" s="3" t="s">
+      <c r="F236" s="9">
+        <v>0</v>
+      </c>
+      <c r="G236" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H236" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I236" t="s">
+      <c r="H236" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I236" s="1" t="s">
         <v>525</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -10399,32 +10399,32 @@
         <v>529</v>
       </c>
     </row>
-    <row r="239" spans="1:9">
-      <c r="A239" s="3" t="s">
+    <row r="239" s="1" customFormat="1" spans="1:9">
+      <c r="A239" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="B239" s="3" t="s">
+      <c r="B239" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C239" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D239" s="4">
+      <c r="C239" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D239" s="8">
         <v>1300</v>
       </c>
-      <c r="E239" s="3">
+      <c r="E239" s="7">
         <v>20</v>
       </c>
-      <c r="F239" s="5">
-        <v>0</v>
-      </c>
-      <c r="G239" s="3" t="s">
+      <c r="F239" s="9">
+        <v>0</v>
+      </c>
+      <c r="G239" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H239" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I239" t="s">
+      <c r="H239" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I239" s="1" t="s">
         <v>531</v>
       </c>
     </row>
@@ -10457,32 +10457,32 @@
         <v>533</v>
       </c>
     </row>
-    <row r="241" spans="1:9">
-      <c r="A241" s="3" t="s">
+    <row r="241" s="1" customFormat="1" spans="1:9">
+      <c r="A241" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="B241" s="3" t="s">
+      <c r="B241" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C241" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D241" s="4">
+      <c r="C241" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D241" s="8">
         <v>1300</v>
       </c>
-      <c r="E241" s="3">
+      <c r="E241" s="7">
         <v>20</v>
       </c>
-      <c r="F241" s="5">
+      <c r="F241" s="9">
         <v>0.02</v>
       </c>
-      <c r="G241" s="3" t="s">
+      <c r="G241" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H241" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I241" t="s">
+      <c r="H241" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I241" s="1" t="s">
         <v>521</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -12777,32 +12777,32 @@
         <v>658</v>
       </c>
     </row>
-    <row r="321" spans="1:9">
-      <c r="A321" s="3" t="s">
+    <row r="321" s="1" customFormat="1" spans="1:9">
+      <c r="A321" s="7" t="s">
         <v>659</v>
       </c>
-      <c r="B321" s="3" t="s">
+      <c r="B321" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C321" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D321" s="4">
+      <c r="C321" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D321" s="8">
         <v>1000</v>
       </c>
-      <c r="E321" s="3">
+      <c r="E321" s="7">
         <v>5</v>
       </c>
-      <c r="F321" s="5">
-        <v>0</v>
-      </c>
-      <c r="G321" s="3" t="s">
+      <c r="F321" s="9">
+        <v>0</v>
+      </c>
+      <c r="G321" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H321" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I321" t="s">
+      <c r="H321" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I321" s="1" t="s">
         <v>660</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -12806,32 +12806,32 @@
         <v>660</v>
       </c>
     </row>
-    <row r="322" spans="1:9">
-      <c r="A322" s="3" t="s">
+    <row r="322" s="1" customFormat="1" spans="1:9">
+      <c r="A322" s="7" t="s">
         <v>661</v>
       </c>
-      <c r="B322" s="3" t="s">
+      <c r="B322" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C322" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D322" s="4">
+      <c r="C322" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D322" s="8">
         <v>1000</v>
       </c>
-      <c r="E322" s="3">
+      <c r="E322" s="7">
         <v>7</v>
       </c>
-      <c r="F322" s="5">
-        <v>0</v>
-      </c>
-      <c r="G322" s="3" t="s">
+      <c r="F322" s="9">
+        <v>0</v>
+      </c>
+      <c r="G322" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H322" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I322" t="s">
+      <c r="H322" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I322" s="1" t="s">
         <v>662</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -12864,32 +12864,32 @@
         <v>664</v>
       </c>
     </row>
-    <row r="324" spans="1:9">
-      <c r="A324" s="3" t="s">
+    <row r="324" s="1" customFormat="1" spans="1:9">
+      <c r="A324" s="7" t="s">
         <v>665</v>
       </c>
-      <c r="B324" s="3" t="s">
+      <c r="B324" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C324" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D324" s="4">
+      <c r="C324" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D324" s="8">
         <v>1000</v>
       </c>
-      <c r="E324" s="3">
-        <v>11</v>
-      </c>
-      <c r="F324" s="5">
-        <v>0</v>
-      </c>
-      <c r="G324" s="3" t="s">
+      <c r="E324" s="7">
+        <v>11</v>
+      </c>
+      <c r="F324" s="9">
+        <v>0</v>
+      </c>
+      <c r="G324" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H324" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I324" t="s">
+      <c r="H324" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I324" s="1" t="s">
         <v>666</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -12893,32 +12893,32 @@
         <v>666</v>
       </c>
     </row>
-    <row r="325" spans="1:9">
-      <c r="A325" s="3" t="s">
+    <row r="325" s="1" customFormat="1" spans="1:9">
+      <c r="A325" s="7" t="s">
         <v>667</v>
       </c>
-      <c r="B325" s="3" t="s">
+      <c r="B325" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C325" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D325" s="4">
+      <c r="C325" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D325" s="8">
         <v>1000</v>
       </c>
-      <c r="E325" s="3">
+      <c r="E325" s="7">
         <v>13</v>
       </c>
-      <c r="F325" s="5">
-        <v>0</v>
-      </c>
-      <c r="G325" s="3" t="s">
+      <c r="F325" s="9">
+        <v>0</v>
+      </c>
+      <c r="G325" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H325" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I325" t="s">
+      <c r="H325" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I325" s="1" t="s">
         <v>668</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -12922,61 +12922,61 @@
         <v>668</v>
       </c>
     </row>
-    <row r="326" spans="1:9">
-      <c r="A326" s="3" t="s">
+    <row r="326" s="1" customFormat="1" spans="1:9">
+      <c r="A326" s="7" t="s">
         <v>669</v>
       </c>
-      <c r="B326" s="3" t="s">
+      <c r="B326" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C326" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D326" s="4">
+      <c r="C326" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D326" s="8">
         <v>1000</v>
       </c>
-      <c r="E326" s="3">
+      <c r="E326" s="7">
         <v>13</v>
       </c>
-      <c r="F326" s="5">
-        <v>0</v>
-      </c>
-      <c r="G326" s="3" t="s">
+      <c r="F326" s="9">
+        <v>0</v>
+      </c>
+      <c r="G326" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H326" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I326" t="s">
+      <c r="H326" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I326" s="1" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="327" spans="1:9">
-      <c r="A327" s="3" t="s">
+    <row r="327" s="1" customFormat="1" spans="1:9">
+      <c r="A327" s="7" t="s">
         <v>671</v>
       </c>
-      <c r="B327" s="3" t="s">
+      <c r="B327" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C327" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D327" s="4">
+      <c r="C327" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D327" s="8">
         <v>1000</v>
       </c>
-      <c r="E327" s="3">
+      <c r="E327" s="7">
         <v>14</v>
       </c>
-      <c r="F327" s="5">
-        <v>0</v>
-      </c>
-      <c r="G327" s="3" t="s">
+      <c r="F327" s="9">
+        <v>0</v>
+      </c>
+      <c r="G327" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H327" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I327" t="s">
+      <c r="H327" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I327" s="1" t="s">
         <v>64</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -13125,32 +13125,32 @@
         <v>679</v>
       </c>
     </row>
-    <row r="333" spans="1:9">
-      <c r="A333" s="3" t="s">
+    <row r="333" s="1" customFormat="1" spans="1:9">
+      <c r="A333" s="7" t="s">
         <v>680</v>
       </c>
-      <c r="B333" s="3" t="s">
+      <c r="B333" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C333" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D333" s="4">
+      <c r="C333" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D333" s="8">
         <v>1000</v>
       </c>
-      <c r="E333" s="3">
+      <c r="E333" s="7">
         <v>16</v>
       </c>
-      <c r="F333" s="5">
-        <v>0</v>
-      </c>
-      <c r="G333" s="3" t="s">
+      <c r="F333" s="9">
+        <v>0</v>
+      </c>
+      <c r="G333" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H333" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I333" t="s">
+      <c r="H333" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I333" s="1" t="s">
         <v>681</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -13154,32 +13154,32 @@
         <v>681</v>
       </c>
     </row>
-    <row r="334" spans="1:9">
-      <c r="A334" s="3" t="s">
+    <row r="334" s="1" customFormat="1" spans="1:9">
+      <c r="A334" s="7" t="s">
         <v>682</v>
       </c>
-      <c r="B334" s="3" t="s">
+      <c r="B334" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C334" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D334" s="4">
+      <c r="C334" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D334" s="8">
         <v>1000</v>
       </c>
-      <c r="E334" s="3">
+      <c r="E334" s="7">
         <v>16</v>
       </c>
-      <c r="F334" s="5">
-        <v>0</v>
-      </c>
-      <c r="G334" s="3" t="s">
+      <c r="F334" s="9">
+        <v>0</v>
+      </c>
+      <c r="G334" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H334" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I334" t="s">
+      <c r="H334" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I334" s="1" t="s">
         <v>683</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -13328,32 +13328,32 @@
         <v>690</v>
       </c>
     </row>
-    <row r="340" spans="1:9">
-      <c r="A340" s="3" t="s">
+    <row r="340" s="1" customFormat="1" spans="1:9">
+      <c r="A340" s="7" t="s">
         <v>691</v>
       </c>
-      <c r="B340" s="3" t="s">
+      <c r="B340" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C340" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D340" s="4">
+      <c r="C340" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D340" s="8">
         <v>1000</v>
       </c>
-      <c r="E340" s="3">
+      <c r="E340" s="7">
         <v>17</v>
       </c>
-      <c r="F340" s="5">
-        <v>0</v>
-      </c>
-      <c r="G340" s="3" t="s">
+      <c r="F340" s="9">
+        <v>0</v>
+      </c>
+      <c r="G340" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H340" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I340" t="s">
+      <c r="H340" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I340" s="1" t="s">
         <v>692</v>
       </c>
     </row>
@@ -13415,32 +13415,32 @@
         <v>360</v>
       </c>
     </row>
-    <row r="343" spans="1:9">
-      <c r="A343" s="3" t="s">
+    <row r="343" s="1" customFormat="1" spans="1:9">
+      <c r="A343" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="B343" s="3" t="s">
+      <c r="B343" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C343" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D343" s="4">
+      <c r="C343" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D343" s="8">
         <v>1000</v>
       </c>
-      <c r="E343" s="3">
+      <c r="E343" s="7">
         <v>18</v>
       </c>
-      <c r="F343" s="5">
-        <v>0</v>
-      </c>
-      <c r="G343" s="3" t="s">
+      <c r="F343" s="9">
+        <v>0</v>
+      </c>
+      <c r="G343" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H343" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I343" t="s">
+      <c r="H343" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I343" s="1" t="s">
         <v>697</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -13851,32 +13851,32 @@
         <v>712</v>
       </c>
     </row>
-    <row r="354" spans="1:9">
-      <c r="A354" s="3" t="s">
+    <row r="354" s="1" customFormat="1" spans="1:9">
+      <c r="A354" s="7" t="s">
         <v>713</v>
       </c>
-      <c r="B354" s="3" t="s">
+      <c r="B354" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C354" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D354" s="4">
+      <c r="C354" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D354" s="8">
         <v>1000</v>
       </c>
-      <c r="E354" s="3">
+      <c r="E354" s="7">
         <v>20</v>
       </c>
-      <c r="F354" s="5">
-        <v>0</v>
-      </c>
-      <c r="G354" s="3" t="s">
+      <c r="F354" s="9">
+        <v>0</v>
+      </c>
+      <c r="G354" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H354" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I354" t="s">
+      <c r="H354" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I354" s="1" t="s">
         <v>64</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="关键词清单" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">关键词清单!$A$1:$I$417</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -3103,12 +3106,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3599,7 +3602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I417"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
@@ -3701,36 +3704,36 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:9">
-      <c r="A4" s="3" t="s">
+    <row r="4" s="1" customFormat="1" spans="1:9">
+      <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="C4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="7">
         <v>49500</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="6">
         <v>29</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="8">
         <v>0.68</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:9">
+    <row r="5" spans="1:9">
       <c r="A5" s="3" t="s">
         <v>26</v>
       </c>
@@ -3817,7 +3820,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:9">
+    <row r="8" spans="1:9">
       <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
@@ -3904,7 +3907,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:9">
+    <row r="11" spans="1:9">
       <c r="A11" s="3" t="s">
         <v>47</v>
       </c>
@@ -3933,7 +3936,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:9">
+    <row r="12" spans="1:9">
       <c r="A12" s="3" t="s">
         <v>50</v>
       </c>
@@ -3962,7 +3965,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:9">
+    <row r="13" spans="1:9">
       <c r="A13" s="3" t="s">
         <v>53</v>
       </c>
@@ -3991,7 +3994,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:9">
+    <row r="14" spans="1:9">
       <c r="A14" s="3" t="s">
         <v>56</v>
       </c>
@@ -4078,7 +4081,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:9">
+    <row r="17" spans="1:9">
       <c r="A17" s="3" t="s">
         <v>65</v>
       </c>
@@ -4107,7 +4110,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:9">
+    <row r="18" spans="1:9">
       <c r="A18" s="3" t="s">
         <v>68</v>
       </c>
@@ -4136,7 +4139,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:9">
+    <row r="19" spans="1:9">
       <c r="A19" s="3" t="s">
         <v>70</v>
       </c>
@@ -4165,7 +4168,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:9">
+    <row r="20" spans="1:9">
       <c r="A20" s="3" t="s">
         <v>73</v>
       </c>
@@ -4194,7 +4197,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:9">
+    <row r="21" spans="1:9">
       <c r="A21" s="3" t="s">
         <v>74</v>
       </c>
@@ -4368,7 +4371,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:9">
+    <row r="27" spans="1:9">
       <c r="A27" s="3" t="s">
         <v>92</v>
       </c>
@@ -4397,7 +4400,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:9">
+    <row r="28" spans="1:9">
       <c r="A28" s="3" t="s">
         <v>95</v>
       </c>
@@ -4426,7 +4429,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" hidden="1" spans="1:9">
+    <row r="29" spans="1:9">
       <c r="A29" s="3" t="s">
         <v>98</v>
       </c>
@@ -4455,7 +4458,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:9">
+    <row r="30" spans="1:9">
       <c r="A30" s="3" t="s">
         <v>100</v>
       </c>
@@ -4658,36 +4661,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" spans="1:9">
-      <c r="A37" s="7" t="s">
+    <row r="37" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A37" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" s="8">
+      <c r="C37" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="7">
         <v>5400</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="6">
         <v>17</v>
       </c>
-      <c r="F37" s="9">
-        <v>0</v>
-      </c>
-      <c r="G37" s="7" t="s">
+      <c r="F37" s="8">
+        <v>0</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="H37" s="6" t="s">
         <v>118</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:9">
+    <row r="38" spans="1:9">
       <c r="A38" s="3" t="s">
         <v>120</v>
       </c>
@@ -4861,7 +4864,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:9">
+    <row r="44" spans="1:9">
       <c r="A44" s="3" t="s">
         <v>136</v>
       </c>
@@ -4890,7 +4893,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:9">
+    <row r="45" spans="1:9">
       <c r="A45" s="3" t="s">
         <v>138</v>
       </c>
@@ -4919,7 +4922,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:9">
+    <row r="46" spans="1:9">
       <c r="A46" s="3" t="s">
         <v>140</v>
       </c>
@@ -4948,7 +4951,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:9">
+    <row r="47" spans="1:9">
       <c r="A47" s="3" t="s">
         <v>143</v>
       </c>
@@ -4977,7 +4980,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:9">
+    <row r="48" spans="1:9">
       <c r="A48" s="3" t="s">
         <v>146</v>
       </c>
@@ -5006,7 +5009,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:9">
+    <row r="49" spans="1:9">
       <c r="A49" s="3" t="s">
         <v>149</v>
       </c>
@@ -5035,7 +5038,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:9">
+    <row r="50" spans="1:9">
       <c r="A50" s="3" t="s">
         <v>152</v>
       </c>
@@ -5064,7 +5067,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:9">
+    <row r="51" spans="1:9">
       <c r="A51" s="3" t="s">
         <v>155</v>
       </c>
@@ -5238,7 +5241,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:9">
+    <row r="57" spans="1:9">
       <c r="A57" s="3" t="s">
         <v>169</v>
       </c>
@@ -5267,7 +5270,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:9">
+    <row r="58" spans="1:9">
       <c r="A58" s="3" t="s">
         <v>171</v>
       </c>
@@ -5296,7 +5299,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:9">
+    <row r="59" spans="1:9">
       <c r="A59" s="3" t="s">
         <v>173</v>
       </c>
@@ -5325,7 +5328,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:9">
+    <row r="60" spans="1:9">
       <c r="A60" s="3" t="s">
         <v>174</v>
       </c>
@@ -5354,7 +5357,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:9">
+    <row r="61" spans="1:9">
       <c r="A61" s="3" t="s">
         <v>176</v>
       </c>
@@ -5383,7 +5386,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:9">
+    <row r="62" spans="1:9">
       <c r="A62" s="3" t="s">
         <v>178</v>
       </c>
@@ -5412,7 +5415,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:9">
+    <row r="63" spans="1:9">
       <c r="A63" s="3" t="s">
         <v>181</v>
       </c>
@@ -5847,7 +5850,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:9">
+    <row r="78" spans="1:9">
       <c r="A78" s="3" t="s">
         <v>217</v>
       </c>
@@ -5876,7 +5879,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:9">
+    <row r="79" spans="1:9">
       <c r="A79" s="3" t="s">
         <v>220</v>
       </c>
@@ -5905,7 +5908,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:9">
+    <row r="80" spans="1:9">
       <c r="A80" s="3" t="s">
         <v>222</v>
       </c>
@@ -5934,7 +5937,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:9">
+    <row r="81" spans="1:9">
       <c r="A81" s="3" t="s">
         <v>224</v>
       </c>
@@ -5963,7 +5966,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:9">
+    <row r="82" spans="1:9">
       <c r="A82" s="3" t="s">
         <v>227</v>
       </c>
@@ -5992,7 +5995,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:9">
+    <row r="83" spans="1:9">
       <c r="A83" s="3" t="s">
         <v>228</v>
       </c>
@@ -6021,7 +6024,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:9">
+    <row r="84" spans="1:9">
       <c r="A84" s="3" t="s">
         <v>231</v>
       </c>
@@ -6050,7 +6053,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:9">
+    <row r="85" spans="1:9">
       <c r="A85" s="3" t="s">
         <v>234</v>
       </c>
@@ -6079,7 +6082,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:9">
+    <row r="86" spans="1:9">
       <c r="A86" s="3" t="s">
         <v>236</v>
       </c>
@@ -6108,7 +6111,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:9">
+    <row r="87" spans="1:9">
       <c r="A87" s="3" t="s">
         <v>239</v>
       </c>
@@ -6427,94 +6430,94 @@
         <v>265</v>
       </c>
     </row>
-    <row r="98" s="1" customFormat="1" spans="1:9">
-      <c r="A98" s="7" t="s">
+    <row r="98" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A98" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="B98" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C98" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D98" s="8">
+      <c r="C98" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D98" s="7">
         <v>2400</v>
       </c>
-      <c r="E98" s="7">
+      <c r="E98" s="6">
         <v>18</v>
       </c>
-      <c r="F98" s="9">
-        <v>0</v>
-      </c>
-      <c r="G98" s="7" t="s">
+      <c r="F98" s="8">
+        <v>0</v>
+      </c>
+      <c r="G98" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H98" s="7" t="s">
+      <c r="H98" s="6" t="s">
         <v>267</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="99" s="1" customFormat="1" spans="1:9">
-      <c r="A99" s="7" t="s">
+    <row r="99" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A99" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B99" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C99" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D99" s="8">
+      <c r="C99" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D99" s="7">
         <v>2400</v>
       </c>
-      <c r="E99" s="7">
+      <c r="E99" s="6">
         <v>19</v>
       </c>
-      <c r="F99" s="9">
-        <v>0</v>
-      </c>
-      <c r="G99" s="7" t="s">
+      <c r="F99" s="8">
+        <v>0</v>
+      </c>
+      <c r="G99" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H99" s="7" t="s">
+      <c r="H99" s="6" t="s">
         <v>269</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="100" s="1" customFormat="1" spans="1:9">
-      <c r="A100" s="7" t="s">
+    <row r="100" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A100" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="B100" s="7" t="s">
+      <c r="B100" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C100" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D100" s="8">
+      <c r="C100" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D100" s="7">
         <v>2400</v>
       </c>
-      <c r="E100" s="7">
+      <c r="E100" s="6">
         <v>19</v>
       </c>
-      <c r="F100" s="9">
-        <v>0</v>
-      </c>
-      <c r="G100" s="7" t="s">
+      <c r="F100" s="8">
+        <v>0</v>
+      </c>
+      <c r="G100" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H100" s="7" t="s">
+      <c r="H100" s="6" t="s">
         <v>271</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="1:9">
+    <row r="101" spans="1:9">
       <c r="A101" s="3" t="s">
         <v>272</v>
       </c>
@@ -6543,7 +6546,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:9">
+    <row r="102" spans="1:9">
       <c r="A102" s="3" t="s">
         <v>274</v>
       </c>
@@ -6572,7 +6575,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:9">
+    <row r="103" spans="1:9">
       <c r="A103" s="3" t="s">
         <v>276</v>
       </c>
@@ -6601,7 +6604,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="104" hidden="1" spans="1:9">
+    <row r="104" spans="1:9">
       <c r="A104" s="3" t="s">
         <v>278</v>
       </c>
@@ -6630,7 +6633,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="1:9">
+    <row r="105" spans="1:9">
       <c r="A105" s="3" t="s">
         <v>280</v>
       </c>
@@ -6659,7 +6662,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="1:9">
+    <row r="106" spans="1:9">
       <c r="A106" s="3" t="s">
         <v>282</v>
       </c>
@@ -6688,7 +6691,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="1:9">
+    <row r="107" spans="1:9">
       <c r="A107" s="3" t="s">
         <v>284</v>
       </c>
@@ -6717,7 +6720,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="1:9">
+    <row r="108" spans="1:9">
       <c r="A108" s="3" t="s">
         <v>285</v>
       </c>
@@ -6746,7 +6749,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:9">
+    <row r="109" spans="1:9">
       <c r="A109" s="3" t="s">
         <v>286</v>
       </c>
@@ -6775,7 +6778,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:9">
+    <row r="110" spans="1:9">
       <c r="A110" s="3" t="s">
         <v>288</v>
       </c>
@@ -6804,7 +6807,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="1:9">
+    <row r="111" spans="1:9">
       <c r="A111" s="3" t="s">
         <v>290</v>
       </c>
@@ -6833,7 +6836,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:9">
+    <row r="112" spans="1:9">
       <c r="A112" s="3" t="s">
         <v>292</v>
       </c>
@@ -6862,7 +6865,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="113" hidden="1" spans="1:9">
+    <row r="113" spans="1:9">
       <c r="A113" s="3" t="s">
         <v>293</v>
       </c>
@@ -6891,7 +6894,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="1:9">
+    <row r="114" spans="1:9">
       <c r="A114" s="3" t="s">
         <v>296</v>
       </c>
@@ -6920,7 +6923,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="115" hidden="1" spans="1:9">
+    <row r="115" spans="1:9">
       <c r="A115" s="3" t="s">
         <v>299</v>
       </c>
@@ -6949,7 +6952,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="116" hidden="1" spans="1:9">
+    <row r="116" spans="1:9">
       <c r="A116" s="3" t="s">
         <v>301</v>
       </c>
@@ -6978,7 +6981,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="117" hidden="1" spans="1:9">
+    <row r="117" spans="1:9">
       <c r="A117" s="3" t="s">
         <v>304</v>
       </c>
@@ -7007,7 +7010,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="118" hidden="1" spans="1:9">
+    <row r="118" spans="1:9">
       <c r="A118" s="3" t="s">
         <v>306</v>
       </c>
@@ -7036,7 +7039,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="1:9">
+    <row r="119" spans="1:9">
       <c r="A119" s="3" t="s">
         <v>309</v>
       </c>
@@ -7065,7 +7068,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="120" hidden="1" spans="1:9">
+    <row r="120" spans="1:9">
       <c r="A120" s="3" t="s">
         <v>311</v>
       </c>
@@ -7094,7 +7097,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="121" hidden="1" spans="1:9">
+    <row r="121" spans="1:9">
       <c r="A121" s="3" t="s">
         <v>312</v>
       </c>
@@ -7123,7 +7126,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" hidden="1" spans="1:9">
+    <row r="122" spans="1:9">
       <c r="A122" s="3" t="s">
         <v>314</v>
       </c>
@@ -7152,7 +7155,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="123" hidden="1" spans="1:9">
+    <row r="123" spans="1:9">
       <c r="A123" s="3" t="s">
         <v>317</v>
       </c>
@@ -7442,58 +7445,58 @@
         <v>335</v>
       </c>
     </row>
-    <row r="133" s="1" customFormat="1" spans="1:9">
-      <c r="A133" s="7" t="s">
+    <row r="133" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A133" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="B133" s="7" t="s">
+      <c r="B133" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C133" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D133" s="8">
+      <c r="C133" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D133" s="7">
         <v>1900</v>
       </c>
-      <c r="E133" s="7">
+      <c r="E133" s="6">
         <v>16</v>
       </c>
-      <c r="F133" s="9">
-        <v>0</v>
-      </c>
-      <c r="G133" s="7" t="s">
+      <c r="F133" s="8">
+        <v>0</v>
+      </c>
+      <c r="G133" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H133" s="7" t="s">
+      <c r="H133" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="134" s="1" customFormat="1" spans="1:9">
-      <c r="A134" s="7" t="s">
+    <row r="134" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A134" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="B134" s="7" t="s">
+      <c r="B134" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C134" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D134" s="8">
+      <c r="C134" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D134" s="7">
         <v>1900</v>
       </c>
-      <c r="E134" s="7">
+      <c r="E134" s="6">
         <v>16</v>
       </c>
-      <c r="F134" s="9">
-        <v>0</v>
-      </c>
-      <c r="G134" s="7" t="s">
+      <c r="F134" s="8">
+        <v>0</v>
+      </c>
+      <c r="G134" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H134" s="7" t="s">
+      <c r="H134" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I134" s="1" t="s">
@@ -7529,29 +7532,29 @@
         <v>49</v>
       </c>
     </row>
-    <row r="136" s="1" customFormat="1" spans="1:9">
-      <c r="A136" s="7" t="s">
+    <row r="136" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A136" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="B136" s="7" t="s">
+      <c r="B136" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C136" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D136" s="8">
+      <c r="C136" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D136" s="7">
         <v>1900</v>
       </c>
-      <c r="E136" s="7">
+      <c r="E136" s="6">
         <v>18</v>
       </c>
-      <c r="F136" s="9">
-        <v>0</v>
-      </c>
-      <c r="G136" s="7" t="s">
+      <c r="F136" s="8">
+        <v>0</v>
+      </c>
+      <c r="G136" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H136" s="7" t="s">
+      <c r="H136" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I136" s="1" t="s">
@@ -7587,7 +7590,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="138" hidden="1" spans="1:9">
+    <row r="138" spans="1:9">
       <c r="A138" s="3" t="s">
         <v>345</v>
       </c>
@@ -7616,7 +7619,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="139" hidden="1" spans="1:9">
+    <row r="139" spans="1:9">
       <c r="A139" s="3" t="s">
         <v>346</v>
       </c>
@@ -7645,7 +7648,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="140" hidden="1" spans="1:9">
+    <row r="140" spans="1:9">
       <c r="A140" s="3" t="s">
         <v>348</v>
       </c>
@@ -7674,7 +7677,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="141" hidden="1" spans="1:9">
+    <row r="141" spans="1:9">
       <c r="A141" s="3" t="s">
         <v>350</v>
       </c>
@@ -7703,7 +7706,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="142" hidden="1" spans="1:9">
+    <row r="142" spans="1:9">
       <c r="A142" s="3" t="s">
         <v>353</v>
       </c>
@@ -7732,7 +7735,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="143" hidden="1" spans="1:9">
+    <row r="143" spans="1:9">
       <c r="A143" s="3" t="s">
         <v>355</v>
       </c>
@@ -7761,7 +7764,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="144" hidden="1" spans="1:9">
+    <row r="144" spans="1:9">
       <c r="A144" s="3" t="s">
         <v>357</v>
       </c>
@@ -7790,7 +7793,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="145" hidden="1" spans="1:9">
+    <row r="145" spans="1:9">
       <c r="A145" s="3" t="s">
         <v>358</v>
       </c>
@@ -7819,7 +7822,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="146" hidden="1" spans="1:9">
+    <row r="146" spans="1:9">
       <c r="A146" s="3" t="s">
         <v>361</v>
       </c>
@@ -7848,7 +7851,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="147" hidden="1" spans="1:9">
+    <row r="147" spans="1:9">
       <c r="A147" s="3" t="s">
         <v>362</v>
       </c>
@@ -7877,7 +7880,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="148" hidden="1" spans="1:9">
+    <row r="148" spans="1:9">
       <c r="A148" s="3" t="s">
         <v>365</v>
       </c>
@@ -7906,7 +7909,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="149" hidden="1" spans="1:9">
+    <row r="149" spans="1:9">
       <c r="A149" s="3" t="s">
         <v>367</v>
       </c>
@@ -7935,7 +7938,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="150" hidden="1" spans="1:9">
+    <row r="150" spans="1:9">
       <c r="A150" s="3" t="s">
         <v>369</v>
       </c>
@@ -7964,7 +7967,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="151" hidden="1" spans="1:9">
+    <row r="151" spans="1:9">
       <c r="A151" s="3" t="s">
         <v>370</v>
       </c>
@@ -7993,7 +7996,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="152" hidden="1" spans="1:9">
+    <row r="152" spans="1:9">
       <c r="A152" s="3" t="s">
         <v>373</v>
       </c>
@@ -8428,58 +8431,58 @@
         <v>49</v>
       </c>
     </row>
-    <row r="167" s="1" customFormat="1" spans="1:9">
-      <c r="A167" s="7" t="s">
+    <row r="167" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A167" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="B167" s="7" t="s">
+      <c r="B167" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C167" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D167" s="8">
+      <c r="C167" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D167" s="7">
         <v>1600</v>
       </c>
-      <c r="E167" s="7">
+      <c r="E167" s="6">
         <v>8</v>
       </c>
-      <c r="F167" s="9">
-        <v>0</v>
-      </c>
-      <c r="G167" s="7" t="s">
+      <c r="F167" s="8">
+        <v>0</v>
+      </c>
+      <c r="G167" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H167" s="7" t="s">
+      <c r="H167" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="168" s="1" customFormat="1" spans="1:9">
-      <c r="A168" s="7" t="s">
+    <row r="168" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A168" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="B168" s="7" t="s">
+      <c r="B168" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C168" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D168" s="8">
+      <c r="C168" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D168" s="7">
         <v>1600</v>
       </c>
-      <c r="E168" s="7">
+      <c r="E168" s="6">
         <v>14</v>
       </c>
-      <c r="F168" s="9">
-        <v>0</v>
-      </c>
-      <c r="G168" s="7" t="s">
+      <c r="F168" s="8">
+        <v>0</v>
+      </c>
+      <c r="G168" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H168" s="7" t="s">
+      <c r="H168" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I168" s="1" t="s">
@@ -8515,29 +8518,29 @@
         <v>401</v>
       </c>
     </row>
-    <row r="170" s="1" customFormat="1" spans="1:9">
-      <c r="A170" s="7" t="s">
+    <row r="170" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A170" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="B170" s="7" t="s">
+      <c r="B170" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C170" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D170" s="8">
+      <c r="C170" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D170" s="7">
         <v>1600</v>
       </c>
-      <c r="E170" s="7">
+      <c r="E170" s="6">
         <v>14</v>
       </c>
-      <c r="F170" s="9">
-        <v>0</v>
-      </c>
-      <c r="G170" s="7" t="s">
+      <c r="F170" s="8">
+        <v>0</v>
+      </c>
+      <c r="G170" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H170" s="7" t="s">
+      <c r="H170" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I170" s="1" t="s">
@@ -8602,29 +8605,29 @@
         <v>86</v>
       </c>
     </row>
-    <row r="173" s="1" customFormat="1" spans="1:9">
-      <c r="A173" s="7" t="s">
+    <row r="173" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A173" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="B173" s="7" t="s">
+      <c r="B173" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C173" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D173" s="8">
+      <c r="C173" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D173" s="7">
         <v>1600</v>
       </c>
-      <c r="E173" s="7">
+      <c r="E173" s="6">
         <v>16</v>
       </c>
-      <c r="F173" s="9">
-        <v>0</v>
-      </c>
-      <c r="G173" s="7" t="s">
+      <c r="F173" s="8">
+        <v>0</v>
+      </c>
+      <c r="G173" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H173" s="7" t="s">
+      <c r="H173" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I173" s="1" t="s">
@@ -8660,181 +8663,181 @@
         <v>408</v>
       </c>
     </row>
-    <row r="175" s="1" customFormat="1" spans="1:9">
-      <c r="A175" s="7" t="s">
+    <row r="175" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A175" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="B175" s="7" t="s">
+      <c r="B175" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C175" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D175" s="8">
+      <c r="C175" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D175" s="7">
         <v>1600</v>
       </c>
-      <c r="E175" s="7">
+      <c r="E175" s="6">
         <v>17</v>
       </c>
-      <c r="F175" s="9">
-        <v>0</v>
-      </c>
-      <c r="G175" s="7" t="s">
+      <c r="F175" s="8">
+        <v>0</v>
+      </c>
+      <c r="G175" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H175" s="7" t="s">
+      <c r="H175" s="6" t="s">
         <v>410</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="176" s="1" customFormat="1" spans="1:9">
-      <c r="A176" s="7" t="s">
+    <row r="176" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A176" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="B176" s="7" t="s">
+      <c r="B176" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C176" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D176" s="8">
+      <c r="C176" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D176" s="7">
         <v>1600</v>
       </c>
-      <c r="E176" s="7">
+      <c r="E176" s="6">
         <v>18</v>
       </c>
-      <c r="F176" s="9">
+      <c r="F176" s="8">
         <v>0.34</v>
       </c>
-      <c r="G176" s="7" t="s">
+      <c r="G176" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H176" s="7" t="s">
+      <c r="H176" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="177" s="1" customFormat="1" spans="1:9">
-      <c r="A177" s="7" t="s">
+    <row r="177" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A177" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="B177" s="7" t="s">
+      <c r="B177" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C177" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D177" s="8">
+      <c r="C177" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D177" s="7">
         <v>1600</v>
       </c>
-      <c r="E177" s="7">
+      <c r="E177" s="6">
         <v>19</v>
       </c>
-      <c r="F177" s="9">
-        <v>0</v>
-      </c>
-      <c r="G177" s="7" t="s">
+      <c r="F177" s="8">
+        <v>0</v>
+      </c>
+      <c r="G177" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H177" s="7" t="s">
+      <c r="H177" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="178" s="1" customFormat="1" spans="1:9">
-      <c r="A178" s="7" t="s">
+    <row r="178" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A178" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="B178" s="7" t="s">
+      <c r="B178" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C178" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D178" s="8">
+      <c r="C178" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D178" s="7">
         <v>1600</v>
       </c>
-      <c r="E178" s="7">
+      <c r="E178" s="6">
         <v>20</v>
       </c>
-      <c r="F178" s="9">
-        <v>0</v>
-      </c>
-      <c r="G178" s="7" t="s">
+      <c r="F178" s="8">
+        <v>0</v>
+      </c>
+      <c r="G178" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H178" s="7" t="s">
+      <c r="H178" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="179" s="1" customFormat="1" spans="1:9">
-      <c r="A179" s="7" t="s">
+    <row r="179" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A179" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="B179" s="7" t="s">
+      <c r="B179" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C179" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D179" s="8">
+      <c r="C179" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D179" s="7">
         <v>1600</v>
       </c>
-      <c r="E179" s="7">
+      <c r="E179" s="6">
         <v>20</v>
       </c>
-      <c r="F179" s="9">
-        <v>0</v>
-      </c>
-      <c r="G179" s="7" t="s">
+      <c r="F179" s="8">
+        <v>0</v>
+      </c>
+      <c r="G179" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H179" s="7" t="s">
+      <c r="H179" s="6" t="s">
         <v>419</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="180" s="1" customFormat="1" spans="1:9">
-      <c r="A180" s="7" t="s">
+    <row r="180" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A180" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="B180" s="7" t="s">
+      <c r="B180" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C180" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D180" s="8">
+      <c r="C180" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D180" s="7">
         <v>1600</v>
       </c>
-      <c r="E180" s="7">
+      <c r="E180" s="6">
         <v>20</v>
       </c>
-      <c r="F180" s="9">
-        <v>0</v>
-      </c>
-      <c r="G180" s="7" t="s">
+      <c r="F180" s="8">
+        <v>0</v>
+      </c>
+      <c r="G180" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H180" s="7" t="s">
+      <c r="H180" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="181" hidden="1" spans="1:9">
+    <row r="181" spans="1:9">
       <c r="A181" s="3" t="s">
         <v>422</v>
       </c>
@@ -8863,7 +8866,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="182" hidden="1" spans="1:9">
+    <row r="182" spans="1:9">
       <c r="A182" s="3" t="s">
         <v>424</v>
       </c>
@@ -8892,7 +8895,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="183" hidden="1" spans="1:9">
+    <row r="183" spans="1:9">
       <c r="A183" s="3" t="s">
         <v>427</v>
       </c>
@@ -8921,7 +8924,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="184" hidden="1" spans="1:9">
+    <row r="184" spans="1:9">
       <c r="A184" s="3" t="s">
         <v>429</v>
       </c>
@@ -8950,7 +8953,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="185" hidden="1" spans="1:9">
+    <row r="185" spans="1:9">
       <c r="A185" s="3" t="s">
         <v>431</v>
       </c>
@@ -8979,7 +8982,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="186" hidden="1" spans="1:9">
+    <row r="186" spans="1:9">
       <c r="A186" s="3" t="s">
         <v>433</v>
       </c>
@@ -9008,7 +9011,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="187" hidden="1" spans="1:9">
+    <row r="187" spans="1:9">
       <c r="A187" s="3" t="s">
         <v>435</v>
       </c>
@@ -9037,7 +9040,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="188" hidden="1" spans="1:9">
+    <row r="188" spans="1:9">
       <c r="A188" s="3" t="s">
         <v>438</v>
       </c>
@@ -9066,7 +9069,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="189" hidden="1" spans="1:9">
+    <row r="189" spans="1:9">
       <c r="A189" s="3" t="s">
         <v>441</v>
       </c>
@@ -9095,7 +9098,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="190" hidden="1" spans="1:9">
+    <row r="190" spans="1:9">
       <c r="A190" s="3" t="s">
         <v>443</v>
       </c>
@@ -9124,7 +9127,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="191" hidden="1" spans="1:9">
+    <row r="191" spans="1:9">
       <c r="A191" s="3" t="s">
         <v>445</v>
       </c>
@@ -9153,7 +9156,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="192" hidden="1" spans="1:9">
+    <row r="192" spans="1:9">
       <c r="A192" s="3" t="s">
         <v>448</v>
       </c>
@@ -9182,7 +9185,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="193" hidden="1" spans="1:9">
+    <row r="193" spans="1:9">
       <c r="A193" s="3" t="s">
         <v>449</v>
       </c>
@@ -9211,7 +9214,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="194" hidden="1" spans="1:9">
+    <row r="194" spans="1:9">
       <c r="A194" s="3" t="s">
         <v>451</v>
       </c>
@@ -9240,7 +9243,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="195" hidden="1" spans="1:9">
+    <row r="195" spans="1:9">
       <c r="A195" s="3" t="s">
         <v>452</v>
       </c>
@@ -9269,7 +9272,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="196" hidden="1" spans="1:9">
+    <row r="196" spans="1:9">
       <c r="A196" s="3" t="s">
         <v>454</v>
       </c>
@@ -9298,7 +9301,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="197" hidden="1" spans="1:9">
+    <row r="197" spans="1:9">
       <c r="A197" s="3" t="s">
         <v>456</v>
       </c>
@@ -9327,7 +9330,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="198" hidden="1" spans="1:9">
+    <row r="198" spans="1:9">
       <c r="A198" s="3" t="s">
         <v>458</v>
       </c>
@@ -9356,7 +9359,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="199" hidden="1" spans="1:9">
+    <row r="199" spans="1:9">
       <c r="A199" s="3" t="s">
         <v>460</v>
       </c>
@@ -9385,7 +9388,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="200" hidden="1" spans="1:9">
+    <row r="200" spans="1:9">
       <c r="A200" s="3" t="s">
         <v>461</v>
       </c>
@@ -9414,7 +9417,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="201" hidden="1" spans="1:9">
+    <row r="201" spans="1:9">
       <c r="A201" s="3" t="s">
         <v>463</v>
       </c>
@@ -9443,7 +9446,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="202" hidden="1" spans="1:9">
+    <row r="202" spans="1:9">
       <c r="A202" s="3" t="s">
         <v>465</v>
       </c>
@@ -9472,7 +9475,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="203" hidden="1" spans="1:9">
+    <row r="203" spans="1:9">
       <c r="A203" s="3" t="s">
         <v>467</v>
       </c>
@@ -10023,29 +10026,29 @@
         <v>500</v>
       </c>
     </row>
-    <row r="222" s="1" customFormat="1" spans="1:9">
-      <c r="A222" s="7" t="s">
+    <row r="222" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A222" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="B222" s="7" t="s">
+      <c r="B222" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C222" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D222" s="8">
+      <c r="C222" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D222" s="7">
         <v>1300</v>
       </c>
-      <c r="E222" s="7">
+      <c r="E222" s="6">
         <v>16</v>
       </c>
-      <c r="F222" s="9">
-        <v>0</v>
-      </c>
-      <c r="G222" s="7" t="s">
+      <c r="F222" s="8">
+        <v>0</v>
+      </c>
+      <c r="G222" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H222" s="7" t="s">
+      <c r="H222" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I222" s="1" t="s">
@@ -10081,87 +10084,87 @@
         <v>49</v>
       </c>
     </row>
-    <row r="224" s="1" customFormat="1" spans="1:9">
-      <c r="A224" s="7" t="s">
+    <row r="224" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A224" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="B224" s="7" t="s">
+      <c r="B224" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C224" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D224" s="8">
+      <c r="C224" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D224" s="7">
         <v>1300</v>
       </c>
-      <c r="E224" s="7">
+      <c r="E224" s="6">
         <v>17</v>
       </c>
-      <c r="F224" s="9">
+      <c r="F224" s="8">
         <v>0.02</v>
       </c>
-      <c r="G224" s="7" t="s">
+      <c r="G224" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H224" s="7" t="s">
+      <c r="H224" s="6" t="s">
         <v>504</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="225" s="1" customFormat="1" spans="1:9">
-      <c r="A225" s="7" t="s">
+    <row r="225" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A225" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="B225" s="7" t="s">
+      <c r="B225" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C225" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D225" s="8">
+      <c r="C225" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D225" s="7">
         <v>1300</v>
       </c>
-      <c r="E225" s="7">
+      <c r="E225" s="6">
         <v>17</v>
       </c>
-      <c r="F225" s="9">
-        <v>0</v>
-      </c>
-      <c r="G225" s="7" t="s">
+      <c r="F225" s="8">
+        <v>0</v>
+      </c>
+      <c r="G225" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H225" s="7" t="s">
+      <c r="H225" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="226" s="1" customFormat="1" spans="1:9">
-      <c r="A226" s="7" t="s">
+    <row r="226" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A226" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="B226" s="7" t="s">
+      <c r="B226" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C226" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D226" s="8">
+      <c r="C226" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D226" s="7">
         <v>1300</v>
       </c>
-      <c r="E226" s="7">
+      <c r="E226" s="6">
         <v>17</v>
       </c>
-      <c r="F226" s="9">
+      <c r="F226" s="8">
         <v>0.03</v>
       </c>
-      <c r="G226" s="7" t="s">
+      <c r="G226" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H226" s="7" t="s">
+      <c r="H226" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I226" s="1" t="s">
@@ -10284,58 +10287,58 @@
         <v>49</v>
       </c>
     </row>
-    <row r="231" s="1" customFormat="1" spans="1:9">
-      <c r="A231" s="7" t="s">
+    <row r="231" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A231" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="B231" s="7" t="s">
+      <c r="B231" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C231" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D231" s="8">
+      <c r="C231" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D231" s="7">
         <v>1300</v>
       </c>
-      <c r="E231" s="7">
+      <c r="E231" s="6">
         <v>19</v>
       </c>
-      <c r="F231" s="9">
-        <v>0</v>
-      </c>
-      <c r="G231" s="7" t="s">
+      <c r="F231" s="8">
+        <v>0</v>
+      </c>
+      <c r="G231" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H231" s="7" t="s">
+      <c r="H231" s="6" t="s">
         <v>515</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="232" s="1" customFormat="1" spans="1:9">
-      <c r="A232" s="7" t="s">
+    <row r="232" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A232" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="B232" s="7" t="s">
+      <c r="B232" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C232" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D232" s="8">
+      <c r="C232" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D232" s="7">
         <v>1300</v>
       </c>
-      <c r="E232" s="7">
+      <c r="E232" s="6">
         <v>19</v>
       </c>
-      <c r="F232" s="9">
-        <v>0</v>
-      </c>
-      <c r="G232" s="7" t="s">
+      <c r="F232" s="8">
+        <v>0</v>
+      </c>
+      <c r="G232" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H232" s="7" t="s">
+      <c r="H232" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I232" s="1" t="s">
@@ -10371,29 +10374,29 @@
         <v>86</v>
       </c>
     </row>
-    <row r="234" s="1" customFormat="1" spans="1:9">
-      <c r="A234" s="7" t="s">
+    <row r="234" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A234" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="B234" s="7" t="s">
+      <c r="B234" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C234" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D234" s="8">
+      <c r="C234" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D234" s="7">
         <v>1300</v>
       </c>
-      <c r="E234" s="7">
+      <c r="E234" s="6">
         <v>20</v>
       </c>
-      <c r="F234" s="9">
+      <c r="F234" s="8">
         <v>0.02</v>
       </c>
-      <c r="G234" s="7" t="s">
+      <c r="G234" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H234" s="7" t="s">
+      <c r="H234" s="6" t="s">
         <v>520</v>
       </c>
       <c r="I234" s="1" t="s">
@@ -10429,29 +10432,29 @@
         <v>523</v>
       </c>
     </row>
-    <row r="236" s="1" customFormat="1" spans="1:9">
-      <c r="A236" s="7" t="s">
+    <row r="236" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A236" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="B236" s="7" t="s">
+      <c r="B236" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C236" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D236" s="8">
+      <c r="C236" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D236" s="7">
         <v>1300</v>
       </c>
-      <c r="E236" s="7">
+      <c r="E236" s="6">
         <v>20</v>
       </c>
-      <c r="F236" s="9">
-        <v>0</v>
-      </c>
-      <c r="G236" s="7" t="s">
+      <c r="F236" s="8">
+        <v>0</v>
+      </c>
+      <c r="G236" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H236" s="7" t="s">
+      <c r="H236" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I236" s="1" t="s">
@@ -10516,29 +10519,29 @@
         <v>529</v>
       </c>
     </row>
-    <row r="239" s="1" customFormat="1" spans="1:9">
-      <c r="A239" s="7" t="s">
+    <row r="239" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A239" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="B239" s="7" t="s">
+      <c r="B239" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C239" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D239" s="8">
+      <c r="C239" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D239" s="7">
         <v>1300</v>
       </c>
-      <c r="E239" s="7">
+      <c r="E239" s="6">
         <v>20</v>
       </c>
-      <c r="F239" s="9">
-        <v>0</v>
-      </c>
-      <c r="G239" s="7" t="s">
+      <c r="F239" s="8">
+        <v>0</v>
+      </c>
+      <c r="G239" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H239" s="7" t="s">
+      <c r="H239" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I239" s="1" t="s">
@@ -10574,29 +10577,29 @@
         <v>533</v>
       </c>
     </row>
-    <row r="241" s="1" customFormat="1" spans="1:9">
-      <c r="A241" s="7" t="s">
+    <row r="241" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A241" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="B241" s="7" t="s">
+      <c r="B241" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C241" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D241" s="8">
+      <c r="C241" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D241" s="7">
         <v>1300</v>
       </c>
-      <c r="E241" s="7">
+      <c r="E241" s="6">
         <v>20</v>
       </c>
-      <c r="F241" s="9">
+      <c r="F241" s="8">
         <v>0.02</v>
       </c>
-      <c r="G241" s="7" t="s">
+      <c r="G241" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H241" s="7" t="s">
+      <c r="H241" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I241" s="1" t="s">
@@ -10661,7 +10664,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="244" hidden="1" spans="1:9">
+    <row r="244" spans="1:9">
       <c r="A244" s="3" t="s">
         <v>539</v>
       </c>
@@ -10690,7 +10693,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="245" hidden="1" spans="1:9">
+    <row r="245" spans="1:9">
       <c r="A245" s="3" t="s">
         <v>542</v>
       </c>
@@ -10719,7 +10722,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="246" hidden="1" spans="1:9">
+    <row r="246" spans="1:9">
       <c r="A246" s="3" t="s">
         <v>543</v>
       </c>
@@ -10748,7 +10751,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="247" hidden="1" spans="1:9">
+    <row r="247" spans="1:9">
       <c r="A247" s="3" t="s">
         <v>544</v>
       </c>
@@ -10777,7 +10780,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="248" hidden="1" spans="1:9">
+    <row r="248" spans="1:9">
       <c r="A248" s="3" t="s">
         <v>545</v>
       </c>
@@ -10806,7 +10809,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="249" hidden="1" spans="1:9">
+    <row r="249" spans="1:9">
       <c r="A249" s="3" t="s">
         <v>546</v>
       </c>
@@ -10835,7 +10838,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="250" hidden="1" spans="1:9">
+    <row r="250" spans="1:9">
       <c r="A250" s="3" t="s">
         <v>548</v>
       </c>
@@ -10864,7 +10867,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="251" hidden="1" spans="1:9">
+    <row r="251" spans="1:9">
       <c r="A251" s="3" t="s">
         <v>550</v>
       </c>
@@ -10893,7 +10896,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="252" hidden="1" spans="1:9">
+    <row r="252" spans="1:9">
       <c r="A252" s="3" t="s">
         <v>552</v>
       </c>
@@ -10922,7 +10925,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="253" hidden="1" spans="1:9">
+    <row r="253" spans="1:9">
       <c r="A253" s="3" t="s">
         <v>553</v>
       </c>
@@ -10951,7 +10954,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="254" hidden="1" spans="1:9">
+    <row r="254" spans="1:9">
       <c r="A254" s="3" t="s">
         <v>555</v>
       </c>
@@ -10980,7 +10983,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="255" hidden="1" spans="1:9">
+    <row r="255" spans="1:9">
       <c r="A255" s="3" t="s">
         <v>556</v>
       </c>
@@ -11009,7 +11012,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="256" hidden="1" spans="1:9">
+    <row r="256" spans="1:9">
       <c r="A256" s="3" t="s">
         <v>557</v>
       </c>
@@ -11038,7 +11041,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="257" hidden="1" spans="1:9">
+    <row r="257" spans="1:9">
       <c r="A257" s="3" t="s">
         <v>560</v>
       </c>
@@ -11067,7 +11070,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="258" hidden="1" spans="1:9">
+    <row r="258" spans="1:9">
       <c r="A258" s="3" t="s">
         <v>561</v>
       </c>
@@ -11096,7 +11099,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="259" hidden="1" spans="1:9">
+    <row r="259" spans="1:9">
       <c r="A259" s="3" t="s">
         <v>564</v>
       </c>
@@ -11125,7 +11128,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="260" hidden="1" spans="1:9">
+    <row r="260" spans="1:9">
       <c r="A260" s="3" t="s">
         <v>565</v>
       </c>
@@ -11154,7 +11157,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="261" hidden="1" spans="1:9">
+    <row r="261" spans="1:9">
       <c r="A261" s="3" t="s">
         <v>567</v>
       </c>
@@ -11183,7 +11186,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="262" hidden="1" spans="1:9">
+    <row r="262" spans="1:9">
       <c r="A262" s="3" t="s">
         <v>568</v>
       </c>
@@ -11212,7 +11215,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="263" hidden="1" spans="1:9">
+    <row r="263" spans="1:9">
       <c r="A263" s="3" t="s">
         <v>570</v>
       </c>
@@ -11241,7 +11244,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="264" hidden="1" spans="1:9">
+    <row r="264" spans="1:9">
       <c r="A264" s="3" t="s">
         <v>572</v>
       </c>
@@ -11270,7 +11273,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="265" hidden="1" spans="1:9">
+    <row r="265" spans="1:9">
       <c r="A265" s="3" t="s">
         <v>574</v>
       </c>
@@ -11299,7 +11302,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="266" hidden="1" spans="1:9">
+    <row r="266" spans="1:9">
       <c r="A266" s="3" t="s">
         <v>576</v>
       </c>
@@ -11328,7 +11331,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="267" hidden="1" spans="1:9">
+    <row r="267" spans="1:9">
       <c r="A267" s="3" t="s">
         <v>577</v>
       </c>
@@ -11357,7 +11360,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="268" hidden="1" spans="1:9">
+    <row r="268" spans="1:9">
       <c r="A268" s="3" t="s">
         <v>579</v>
       </c>
@@ -11386,7 +11389,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="269" hidden="1" spans="1:9">
+    <row r="269" spans="1:9">
       <c r="A269" s="3" t="s">
         <v>581</v>
       </c>
@@ -11415,7 +11418,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="270" hidden="1" spans="1:9">
+    <row r="270" spans="1:9">
       <c r="A270" s="3" t="s">
         <v>583</v>
       </c>
@@ -11444,7 +11447,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="271" hidden="1" spans="1:9">
+    <row r="271" spans="1:9">
       <c r="A271" s="3" t="s">
         <v>584</v>
       </c>
@@ -11473,7 +11476,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="272" hidden="1" spans="1:9">
+    <row r="272" spans="1:9">
       <c r="A272" s="3" t="s">
         <v>585</v>
       </c>
@@ -11502,7 +11505,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="273" hidden="1" spans="1:9">
+    <row r="273" spans="1:9">
       <c r="A273" s="3" t="s">
         <v>587</v>
       </c>
@@ -11531,7 +11534,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="274" hidden="1" spans="1:9">
+    <row r="274" spans="1:9">
       <c r="A274" s="3" t="s">
         <v>589</v>
       </c>
@@ -11560,7 +11563,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="275" hidden="1" spans="1:9">
+    <row r="275" spans="1:9">
       <c r="A275" s="3" t="s">
         <v>590</v>
       </c>
@@ -11589,7 +11592,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="276" hidden="1" spans="1:9">
+    <row r="276" spans="1:9">
       <c r="A276" s="3" t="s">
         <v>591</v>
       </c>
@@ -11618,7 +11621,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="277" hidden="1" spans="1:9">
+    <row r="277" spans="1:9">
       <c r="A277" s="3" t="s">
         <v>592</v>
       </c>
@@ -11647,7 +11650,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="278" hidden="1" spans="1:9">
+    <row r="278" spans="1:9">
       <c r="A278" s="3" t="s">
         <v>594</v>
       </c>
@@ -11676,7 +11679,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="279" hidden="1" spans="1:9">
+    <row r="279" spans="1:9">
       <c r="A279" s="3" t="s">
         <v>596</v>
       </c>
@@ -11705,7 +11708,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="280" hidden="1" spans="1:9">
+    <row r="280" spans="1:9">
       <c r="A280" s="3" t="s">
         <v>597</v>
       </c>
@@ -11734,7 +11737,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="281" hidden="1" spans="1:9">
+    <row r="281" spans="1:9">
       <c r="A281" s="3" t="s">
         <v>599</v>
       </c>
@@ -11763,7 +11766,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="282" hidden="1" spans="1:9">
+    <row r="282" spans="1:9">
       <c r="A282" s="3" t="s">
         <v>600</v>
       </c>
@@ -11792,7 +11795,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="283" hidden="1" spans="1:9">
+    <row r="283" spans="1:9">
       <c r="A283" s="3" t="s">
         <v>601</v>
       </c>
@@ -11821,7 +11824,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="284" hidden="1" spans="1:9">
+    <row r="284" spans="1:9">
       <c r="A284" s="3" t="s">
         <v>603</v>
       </c>
@@ -11850,7 +11853,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="285" hidden="1" spans="1:9">
+    <row r="285" spans="1:9">
       <c r="A285" s="3" t="s">
         <v>604</v>
       </c>
@@ -11879,7 +11882,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="286" hidden="1" spans="1:9">
+    <row r="286" spans="1:9">
       <c r="A286" s="3" t="s">
         <v>605</v>
       </c>
@@ -11908,7 +11911,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="287" hidden="1" spans="1:9">
+    <row r="287" spans="1:9">
       <c r="A287" s="3" t="s">
         <v>606</v>
       </c>
@@ -11937,7 +11940,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="288" hidden="1" spans="1:9">
+    <row r="288" spans="1:9">
       <c r="A288" s="3" t="s">
         <v>607</v>
       </c>
@@ -11966,7 +11969,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="289" hidden="1" spans="1:9">
+    <row r="289" spans="1:9">
       <c r="A289" s="3" t="s">
         <v>609</v>
       </c>
@@ -11995,7 +11998,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="290" hidden="1" spans="1:9">
+    <row r="290" spans="1:9">
       <c r="A290" s="3" t="s">
         <v>611</v>
       </c>
@@ -12024,7 +12027,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="291" hidden="1" spans="1:9">
+    <row r="291" spans="1:9">
       <c r="A291" s="3" t="s">
         <v>612</v>
       </c>
@@ -12053,7 +12056,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="292" hidden="1" spans="1:9">
+    <row r="292" spans="1:9">
       <c r="A292" s="3" t="s">
         <v>615</v>
       </c>
@@ -12082,7 +12085,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="293" hidden="1" spans="1:9">
+    <row r="293" spans="1:9">
       <c r="A293" s="3" t="s">
         <v>617</v>
       </c>
@@ -12111,7 +12114,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="294" hidden="1" spans="1:9">
+    <row r="294" spans="1:9">
       <c r="A294" s="3" t="s">
         <v>618</v>
       </c>
@@ -12894,58 +12897,58 @@
         <v>658</v>
       </c>
     </row>
-    <row r="321" s="1" customFormat="1" spans="1:9">
-      <c r="A321" s="7" t="s">
+    <row r="321" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A321" s="6" t="s">
         <v>659</v>
       </c>
-      <c r="B321" s="7" t="s">
+      <c r="B321" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C321" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D321" s="8">
+      <c r="C321" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D321" s="7">
         <v>1000</v>
       </c>
-      <c r="E321" s="7">
+      <c r="E321" s="6">
         <v>5</v>
       </c>
-      <c r="F321" s="9">
-        <v>0</v>
-      </c>
-      <c r="G321" s="7" t="s">
+      <c r="F321" s="8">
+        <v>0</v>
+      </c>
+      <c r="G321" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H321" s="7" t="s">
+      <c r="H321" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="322" s="1" customFormat="1" spans="1:9">
-      <c r="A322" s="7" t="s">
+    <row r="322" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A322" s="6" t="s">
         <v>661</v>
       </c>
-      <c r="B322" s="7" t="s">
+      <c r="B322" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C322" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D322" s="8">
+      <c r="C322" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D322" s="7">
         <v>1000</v>
       </c>
-      <c r="E322" s="7">
+      <c r="E322" s="6">
         <v>7</v>
       </c>
-      <c r="F322" s="9">
-        <v>0</v>
-      </c>
-      <c r="G322" s="7" t="s">
+      <c r="F322" s="8">
+        <v>0</v>
+      </c>
+      <c r="G322" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H322" s="7" t="s">
+      <c r="H322" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I322" s="1" t="s">
@@ -12981,116 +12984,116 @@
         <v>664</v>
       </c>
     </row>
-    <row r="324" s="1" customFormat="1" spans="1:9">
-      <c r="A324" s="7" t="s">
+    <row r="324" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A324" s="6" t="s">
         <v>665</v>
       </c>
-      <c r="B324" s="7" t="s">
+      <c r="B324" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C324" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D324" s="8">
+      <c r="C324" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D324" s="7">
         <v>1000</v>
       </c>
-      <c r="E324" s="7">
-        <v>11</v>
-      </c>
-      <c r="F324" s="9">
-        <v>0</v>
-      </c>
-      <c r="G324" s="7" t="s">
+      <c r="E324" s="6">
+        <v>11</v>
+      </c>
+      <c r="F324" s="8">
+        <v>0</v>
+      </c>
+      <c r="G324" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H324" s="7" t="s">
+      <c r="H324" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="325" s="1" customFormat="1" spans="1:9">
-      <c r="A325" s="7" t="s">
+    <row r="325" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A325" s="6" t="s">
         <v>667</v>
       </c>
-      <c r="B325" s="7" t="s">
+      <c r="B325" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C325" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D325" s="8">
+      <c r="C325" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D325" s="7">
         <v>1000</v>
       </c>
-      <c r="E325" s="7">
+      <c r="E325" s="6">
         <v>13</v>
       </c>
-      <c r="F325" s="9">
-        <v>0</v>
-      </c>
-      <c r="G325" s="7" t="s">
+      <c r="F325" s="8">
+        <v>0</v>
+      </c>
+      <c r="G325" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H325" s="7" t="s">
+      <c r="H325" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="326" s="1" customFormat="1" spans="1:9">
-      <c r="A326" s="7" t="s">
+    <row r="326" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A326" s="6" t="s">
         <v>669</v>
       </c>
-      <c r="B326" s="7" t="s">
+      <c r="B326" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C326" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D326" s="8">
+      <c r="C326" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D326" s="7">
         <v>1000</v>
       </c>
-      <c r="E326" s="7">
+      <c r="E326" s="6">
         <v>13</v>
       </c>
-      <c r="F326" s="9">
-        <v>0</v>
-      </c>
-      <c r="G326" s="7" t="s">
+      <c r="F326" s="8">
+        <v>0</v>
+      </c>
+      <c r="G326" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H326" s="7" t="s">
+      <c r="H326" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="327" s="1" customFormat="1" spans="1:9">
-      <c r="A327" s="7" t="s">
+    <row r="327" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A327" s="6" t="s">
         <v>671</v>
       </c>
-      <c r="B327" s="7" t="s">
+      <c r="B327" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C327" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D327" s="8">
+      <c r="C327" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D327" s="7">
         <v>1000</v>
       </c>
-      <c r="E327" s="7">
+      <c r="E327" s="6">
         <v>14</v>
       </c>
-      <c r="F327" s="9">
-        <v>0</v>
-      </c>
-      <c r="G327" s="7" t="s">
+      <c r="F327" s="8">
+        <v>0</v>
+      </c>
+      <c r="G327" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H327" s="7" t="s">
+      <c r="H327" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I327" s="1" t="s">
@@ -13242,58 +13245,58 @@
         <v>679</v>
       </c>
     </row>
-    <row r="333" s="1" customFormat="1" spans="1:9">
-      <c r="A333" s="7" t="s">
+    <row r="333" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A333" s="6" t="s">
         <v>680</v>
       </c>
-      <c r="B333" s="7" t="s">
+      <c r="B333" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C333" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D333" s="8">
+      <c r="C333" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D333" s="7">
         <v>1000</v>
       </c>
-      <c r="E333" s="7">
+      <c r="E333" s="6">
         <v>16</v>
       </c>
-      <c r="F333" s="9">
-        <v>0</v>
-      </c>
-      <c r="G333" s="7" t="s">
+      <c r="F333" s="8">
+        <v>0</v>
+      </c>
+      <c r="G333" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H333" s="7" t="s">
+      <c r="H333" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="334" s="1" customFormat="1" spans="1:9">
-      <c r="A334" s="7" t="s">
+    <row r="334" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A334" s="6" t="s">
         <v>682</v>
       </c>
-      <c r="B334" s="7" t="s">
+      <c r="B334" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C334" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D334" s="8">
+      <c r="C334" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D334" s="7">
         <v>1000</v>
       </c>
-      <c r="E334" s="7">
+      <c r="E334" s="6">
         <v>16</v>
       </c>
-      <c r="F334" s="9">
-        <v>0</v>
-      </c>
-      <c r="G334" s="7" t="s">
+      <c r="F334" s="8">
+        <v>0</v>
+      </c>
+      <c r="G334" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H334" s="7" t="s">
+      <c r="H334" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I334" s="1" t="s">
@@ -13445,29 +13448,29 @@
         <v>690</v>
       </c>
     </row>
-    <row r="340" s="1" customFormat="1" spans="1:9">
-      <c r="A340" s="7" t="s">
+    <row r="340" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A340" s="6" t="s">
         <v>691</v>
       </c>
-      <c r="B340" s="7" t="s">
+      <c r="B340" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C340" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D340" s="8">
+      <c r="C340" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D340" s="7">
         <v>1000</v>
       </c>
-      <c r="E340" s="7">
+      <c r="E340" s="6">
         <v>17</v>
       </c>
-      <c r="F340" s="9">
-        <v>0</v>
-      </c>
-      <c r="G340" s="7" t="s">
+      <c r="F340" s="8">
+        <v>0</v>
+      </c>
+      <c r="G340" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H340" s="7" t="s">
+      <c r="H340" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I340" s="1" t="s">
@@ -13532,29 +13535,29 @@
         <v>360</v>
       </c>
     </row>
-    <row r="343" s="1" customFormat="1" spans="1:9">
-      <c r="A343" s="7" t="s">
+    <row r="343" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A343" s="6" t="s">
         <v>696</v>
       </c>
-      <c r="B343" s="7" t="s">
+      <c r="B343" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C343" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D343" s="8">
+      <c r="C343" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D343" s="7">
         <v>1000</v>
       </c>
-      <c r="E343" s="7">
+      <c r="E343" s="6">
         <v>18</v>
       </c>
-      <c r="F343" s="9">
-        <v>0</v>
-      </c>
-      <c r="G343" s="7" t="s">
+      <c r="F343" s="8">
+        <v>0</v>
+      </c>
+      <c r="G343" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H343" s="7" t="s">
+      <c r="H343" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I343" s="1" t="s">
@@ -13648,29 +13651,29 @@
         <v>408</v>
       </c>
     </row>
-    <row r="347" s="1" customFormat="1" spans="1:9">
-      <c r="A347" s="7" t="s">
+    <row r="347" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A347" s="6" t="s">
         <v>701</v>
       </c>
-      <c r="B347" s="7" t="s">
+      <c r="B347" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C347" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D347" s="8">
+      <c r="C347" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D347" s="7">
         <v>1000</v>
       </c>
-      <c r="E347" s="7">
+      <c r="E347" s="6">
         <v>19</v>
       </c>
-      <c r="F347" s="9">
-        <v>0</v>
-      </c>
-      <c r="G347" s="7" t="s">
+      <c r="F347" s="8">
+        <v>0</v>
+      </c>
+      <c r="G347" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H347" s="7" t="s">
+      <c r="H347" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I347" s="1" t="s">
@@ -13735,58 +13738,58 @@
         <v>49</v>
       </c>
     </row>
-    <row r="350" s="1" customFormat="1" spans="1:9">
-      <c r="A350" s="7" t="s">
+    <row r="350" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A350" s="6" t="s">
         <v>706</v>
       </c>
-      <c r="B350" s="7" t="s">
+      <c r="B350" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C350" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D350" s="8">
+      <c r="C350" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D350" s="7">
         <v>1000</v>
       </c>
-      <c r="E350" s="7">
+      <c r="E350" s="6">
         <v>19</v>
       </c>
-      <c r="F350" s="9">
-        <v>0</v>
-      </c>
-      <c r="G350" s="7" t="s">
+      <c r="F350" s="8">
+        <v>0</v>
+      </c>
+      <c r="G350" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H350" s="7" t="s">
+      <c r="H350" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="351" s="1" customFormat="1" spans="1:9">
-      <c r="A351" s="7" t="s">
+    <row r="351" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A351" s="6" t="s">
         <v>707</v>
       </c>
-      <c r="B351" s="7" t="s">
+      <c r="B351" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C351" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D351" s="8">
+      <c r="C351" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D351" s="7">
         <v>1000</v>
       </c>
-      <c r="E351" s="7">
+      <c r="E351" s="6">
         <v>19</v>
       </c>
-      <c r="F351" s="9">
+      <c r="F351" s="8">
         <v>0.02</v>
       </c>
-      <c r="G351" s="7" t="s">
+      <c r="G351" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H351" s="7" t="s">
+      <c r="H351" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I351" s="1" t="s">
@@ -13851,36 +13854,36 @@
         <v>712</v>
       </c>
     </row>
-    <row r="354" s="1" customFormat="1" spans="1:9">
-      <c r="A354" s="7" t="s">
+    <row r="354" s="1" customFormat="1" hidden="1" spans="1:9">
+      <c r="A354" s="6" t="s">
         <v>713</v>
       </c>
-      <c r="B354" s="7" t="s">
+      <c r="B354" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C354" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D354" s="8">
+      <c r="C354" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D354" s="7">
         <v>1000</v>
       </c>
-      <c r="E354" s="7">
+      <c r="E354" s="6">
         <v>20</v>
       </c>
-      <c r="F354" s="9">
-        <v>0</v>
-      </c>
-      <c r="G354" s="7" t="s">
+      <c r="F354" s="8">
+        <v>0</v>
+      </c>
+      <c r="G354" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H354" s="7" t="s">
+      <c r="H354" s="6" t="s">
         <v>66</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="355" hidden="1" spans="1:9">
+    <row r="355" spans="1:9">
       <c r="A355" s="3" t="s">
         <v>714</v>
       </c>
@@ -13909,7 +13912,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="356" hidden="1" spans="1:9">
+    <row r="356" spans="1:9">
       <c r="A356" s="3" t="s">
         <v>716</v>
       </c>
@@ -13938,7 +13941,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="357" hidden="1" spans="1:9">
+    <row r="357" spans="1:9">
       <c r="A357" s="3" t="s">
         <v>718</v>
       </c>
@@ -13967,7 +13970,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="358" hidden="1" spans="1:9">
+    <row r="358" spans="1:9">
       <c r="A358" s="3" t="s">
         <v>720</v>
       </c>
@@ -13996,7 +13999,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="359" hidden="1" spans="1:9">
+    <row r="359" spans="1:9">
       <c r="A359" s="3" t="s">
         <v>722</v>
       </c>
@@ -14025,7 +14028,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="360" hidden="1" spans="1:9">
+    <row r="360" spans="1:9">
       <c r="A360" s="3" t="s">
         <v>724</v>
       </c>
@@ -14054,7 +14057,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="361" hidden="1" spans="1:9">
+    <row r="361" spans="1:9">
       <c r="A361" s="3" t="s">
         <v>726</v>
       </c>
@@ -14083,7 +14086,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="362" hidden="1" spans="1:9">
+    <row r="362" spans="1:9">
       <c r="A362" s="3" t="s">
         <v>728</v>
       </c>
@@ -14112,7 +14115,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="363" hidden="1" spans="1:9">
+    <row r="363" spans="1:9">
       <c r="A363" s="3" t="s">
         <v>730</v>
       </c>
@@ -14141,7 +14144,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="364" hidden="1" spans="1:9">
+    <row r="364" spans="1:9">
       <c r="A364" s="3" t="s">
         <v>731</v>
       </c>
@@ -14170,7 +14173,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="365" hidden="1" spans="1:9">
+    <row r="365" spans="1:9">
       <c r="A365" s="3" t="s">
         <v>733</v>
       </c>
@@ -14199,7 +14202,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="366" hidden="1" spans="1:9">
+    <row r="366" spans="1:9">
       <c r="A366" s="3" t="s">
         <v>734</v>
       </c>
@@ -14228,7 +14231,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="367" hidden="1" spans="1:9">
+    <row r="367" spans="1:9">
       <c r="A367" s="3" t="s">
         <v>736</v>
       </c>
@@ -14257,7 +14260,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="368" hidden="1" spans="1:9">
+    <row r="368" spans="1:9">
       <c r="A368" s="3" t="s">
         <v>737</v>
       </c>
@@ -14286,7 +14289,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="369" hidden="1" spans="1:9">
+    <row r="369" spans="1:9">
       <c r="A369" s="3" t="s">
         <v>738</v>
       </c>
@@ -14315,7 +14318,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="370" hidden="1" spans="1:9">
+    <row r="370" spans="1:9">
       <c r="A370" s="3" t="s">
         <v>740</v>
       </c>
@@ -14344,7 +14347,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="371" hidden="1" spans="1:9">
+    <row r="371" spans="1:9">
       <c r="A371" s="3" t="s">
         <v>741</v>
       </c>
@@ -14373,7 +14376,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="372" hidden="1" spans="1:9">
+    <row r="372" spans="1:9">
       <c r="A372" s="3" t="s">
         <v>743</v>
       </c>
@@ -14402,7 +14405,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="373" hidden="1" spans="1:9">
+    <row r="373" spans="1:9">
       <c r="A373" s="3" t="s">
         <v>745</v>
       </c>
@@ -14431,7 +14434,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="374" hidden="1" spans="1:9">
+    <row r="374" spans="1:9">
       <c r="A374" s="3" t="s">
         <v>747</v>
       </c>
@@ -14460,7 +14463,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="375" hidden="1" spans="1:9">
+    <row r="375" spans="1:9">
       <c r="A375" s="3" t="s">
         <v>748</v>
       </c>
@@ -14489,7 +14492,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="376" hidden="1" spans="1:9">
+    <row r="376" spans="1:9">
       <c r="A376" s="3" t="s">
         <v>749</v>
       </c>
@@ -14518,7 +14521,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="377" hidden="1" spans="1:9">
+    <row r="377" spans="1:9">
       <c r="A377" s="3" t="s">
         <v>750</v>
       </c>
@@ -14547,7 +14550,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="378" hidden="1" spans="1:9">
+    <row r="378" spans="1:9">
       <c r="A378" s="3" t="s">
         <v>752</v>
       </c>
@@ -14576,7 +14579,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="379" hidden="1" spans="1:9">
+    <row r="379" spans="1:9">
       <c r="A379" s="3" t="s">
         <v>754</v>
       </c>
@@ -14605,7 +14608,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="380" hidden="1" spans="1:9">
+    <row r="380" spans="1:9">
       <c r="A380" s="3" t="s">
         <v>755</v>
       </c>
@@ -14634,7 +14637,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="381" hidden="1" spans="1:9">
+    <row r="381" spans="1:9">
       <c r="A381" s="3" t="s">
         <v>756</v>
       </c>
@@ -14663,7 +14666,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="382" hidden="1" spans="1:9">
+    <row r="382" spans="1:9">
       <c r="A382" s="3" t="s">
         <v>757</v>
       </c>
@@ -14692,7 +14695,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="383" hidden="1" spans="1:9">
+    <row r="383" spans="1:9">
       <c r="A383" s="3" t="s">
         <v>759</v>
       </c>
@@ -14721,7 +14724,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="384" hidden="1" spans="1:9">
+    <row r="384" spans="1:9">
       <c r="A384" s="3" t="s">
         <v>761</v>
       </c>
@@ -14750,7 +14753,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="385" hidden="1" spans="1:9">
+    <row r="385" spans="1:9">
       <c r="A385" s="3" t="s">
         <v>763</v>
       </c>
@@ -14779,7 +14782,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="386" hidden="1" spans="1:9">
+    <row r="386" spans="1:9">
       <c r="A386" s="3" t="s">
         <v>765</v>
       </c>
@@ -14808,7 +14811,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="387" hidden="1" spans="1:9">
+    <row r="387" spans="1:9">
       <c r="A387" s="3" t="s">
         <v>766</v>
       </c>
@@ -14837,7 +14840,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="388" hidden="1" spans="1:9">
+    <row r="388" spans="1:9">
       <c r="A388" s="3" t="s">
         <v>768</v>
       </c>
@@ -14866,7 +14869,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="389" hidden="1" spans="1:9">
+    <row r="389" spans="1:9">
       <c r="A389" s="3" t="s">
         <v>769</v>
       </c>
@@ -14895,7 +14898,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="390" hidden="1" spans="1:9">
+    <row r="390" spans="1:9">
       <c r="A390" s="3" t="s">
         <v>770</v>
       </c>
@@ -14924,7 +14927,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="391" hidden="1" spans="1:9">
+    <row r="391" spans="1:9">
       <c r="A391" s="3" t="s">
         <v>771</v>
       </c>
@@ -14953,7 +14956,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="392" hidden="1" spans="1:9">
+    <row r="392" spans="1:9">
       <c r="A392" s="3" t="s">
         <v>773</v>
       </c>
@@ -14982,7 +14985,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="393" hidden="1" spans="1:9">
+    <row r="393" spans="1:9">
       <c r="A393" s="3" t="s">
         <v>775</v>
       </c>
@@ -15011,7 +15014,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="394" hidden="1" spans="1:9">
+    <row r="394" spans="1:9">
       <c r="A394" s="3" t="s">
         <v>776</v>
       </c>
@@ -15040,7 +15043,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="395" hidden="1" spans="1:9">
+    <row r="395" spans="1:9">
       <c r="A395" s="3" t="s">
         <v>777</v>
       </c>
@@ -15069,7 +15072,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="396" hidden="1" spans="1:9">
+    <row r="396" spans="1:9">
       <c r="A396" s="3" t="s">
         <v>778</v>
       </c>
@@ -15098,7 +15101,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="397" hidden="1" spans="1:9">
+    <row r="397" spans="1:9">
       <c r="A397" s="3" t="s">
         <v>780</v>
       </c>
@@ -15127,7 +15130,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="398" hidden="1" spans="1:9">
+    <row r="398" spans="1:9">
       <c r="A398" s="3" t="s">
         <v>781</v>
       </c>
@@ -15156,7 +15159,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="399" hidden="1" spans="1:9">
+    <row r="399" spans="1:9">
       <c r="A399" s="3" t="s">
         <v>783</v>
       </c>
@@ -15185,7 +15188,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="400" hidden="1" spans="1:9">
+    <row r="400" spans="1:9">
       <c r="A400" s="3" t="s">
         <v>786</v>
       </c>
@@ -15708,6 +15711,14 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I417" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="🟡 第2波"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -3733,32 +3733,32 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="3" t="s">
+    <row r="5" s="1" customFormat="1" spans="1:9">
+      <c r="A5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="7">
         <v>14800</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="6">
         <v>30</v>
       </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="3" t="s">
+      <c r="F5" s="8">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15713,9 +15713,9 @@
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I417" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="6">
-      <filters>
-        <filter val="🟡 第2波"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="🟡 第2波"/>
+      </customFilters>
     </filterColumn>
     <extLst/>
   </autoFilter>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -3820,32 +3820,32 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="3" t="s">
+    <row r="8" s="1" customFormat="1" spans="1:9">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="7">
         <v>12100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="6">
         <v>27</v>
       </c>
-      <c r="F8" s="5">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="1" t="s">
         <v>39</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -3907,32 +3907,32 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="3" t="s">
+    <row r="11" s="1" customFormat="1" spans="1:9">
+      <c r="A11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="C11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="7">
         <v>9900</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="6">
         <v>25</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="8">
         <v>0.02</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="3" t="s">
+      <c r="G11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="1" t="s">
         <v>49</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12840"/>
+    <workbookView windowWidth="30240" windowHeight="12880"/>
   </bookViews>
   <sheets>
     <sheet name="关键词清单" sheetId="1" r:id="rId1"/>
@@ -3936,32 +3936,32 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="3" t="s">
+    <row r="12" s="1" customFormat="1" spans="1:9">
+      <c r="A12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="C12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="7">
         <v>9900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="6">
         <v>25</v>
       </c>
-      <c r="F12" s="5">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="F12" s="8">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="1" t="s">
         <v>52</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12880"/>
+    <workbookView windowWidth="30240" windowHeight="12940"/>
   </bookViews>
   <sheets>
     <sheet name="关键词清单" sheetId="1" r:id="rId1"/>
@@ -3965,32 +3965,32 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="3" t="s">
+    <row r="13" s="1" customFormat="1" spans="1:9">
+      <c r="A13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="C13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="7">
         <v>9900</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="6">
         <v>27</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="8">
         <v>0.25</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="3" t="s">
+      <c r="G13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="1" t="s">
         <v>55</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -3994,32 +3994,32 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="3" t="s">
+    <row r="14" s="1" customFormat="1" spans="1:9">
+      <c r="A14" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="C14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="7">
         <v>9900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="6">
         <v>30</v>
       </c>
-      <c r="F14" s="5">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="F14" s="8">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="1" t="s">
         <v>58</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4081,32 +4081,32 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="3" t="s">
+    <row r="17" s="1" customFormat="1" spans="1:9">
+      <c r="A17" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="C17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="7">
         <v>8100</v>
       </c>
-      <c r="E17" s="3">
-        <v>22</v>
-      </c>
-      <c r="F17" s="5">
+      <c r="E17" s="6">
+        <v>22</v>
+      </c>
+      <c r="F17" s="8">
         <v>0.36</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="G17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>67</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12940"/>
+    <workbookView windowWidth="30240" windowHeight="13060"/>
   </bookViews>
   <sheets>
     <sheet name="关键词清单" sheetId="1" r:id="rId1"/>
@@ -4110,32 +4110,32 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="3" t="s">
+    <row r="18" s="1" customFormat="1" spans="1:9">
+      <c r="A18" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="C18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="7">
         <v>8100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="6">
         <v>25</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="8">
         <v>0.22</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="3" t="s">
+      <c r="G18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="1" t="s">
         <v>14</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -4139,32 +4139,32 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="3" t="s">
+    <row r="19" s="1" customFormat="1" spans="1:9">
+      <c r="A19" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="4">
+      <c r="C19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="7">
         <v>8100</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="6">
         <v>25</v>
       </c>
-      <c r="F19" s="5">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="3" t="s">
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="1" t="s">
         <v>72</v>
       </c>
     </row>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -162,7 +162,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -371,6 +371,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -643,7 +648,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -667,6 +672,10 @@
     <xf numFmtId="3" fontId="3" fillId="35" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="35" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="36" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="36" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1327,41 +1336,41 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>dnd classes</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>⚔️ CLASSES</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>指南页</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n">
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>指南页</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
         <v>60500</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="19" t="n">
         <v>0.02</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>🟢 第1波</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>dnd 5e classes, classes dnd, dnd classes 5e, all dnd classes, dnd character classes</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=y84OYRwzZU8</t>
         </is>

--- a/DND-筛选后关键词清单.xlsx
+++ b/DND-筛选后关键词清单.xlsx
@@ -1459,82 +1459,82 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>dnd backgrounds</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>🗺️ LORE</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>指南页</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>指南页</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="n">
         <v>14800</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="F6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>🔴 第3波</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>dnd 5e backgrounds, dnd backgrounds 5e, backgrounds dnd, dnd background, dnd 2024 backgrounds</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=vyg5jJrZ42s</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>dnd druid</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>⚔️ CLASSES</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>指南页</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>指南页</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
         <v>14800</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="17" t="n">
         <v>34</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>🔴 第3波</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>druid dnd, dnd druid circle of the sea, dnd 5e druid, dnd druid subclasses</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=WMo_gCRMSfA</t>
         </is>
